--- a/outputs/resultats/cibc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/cibc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$K$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K1"/>
+  <dimension ref="A1:N1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -450,6 +450,9 @@
     <col width="70" customWidth="1" min="9" max="9"/>
     <col width="22" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -508,9 +511,24 @@
           <t>Commentaire analyste</t>
         </is>
       </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Statut validation</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Validé par</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Validé le</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
+  <autoFilter ref="A1:N1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/outputs/resultats/cibc/2025_t2_vs_2025_t1/comparison.xlsx
+++ b/outputs/resultats/cibc/2025_t2_vs_2025_t1/comparison.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Changements détectés" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$N$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Changements détectés'!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1"/>
+  <dimension ref="A1:M1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -448,11 +448,10 @@
     <col width="50" customWidth="1" min="7" max="7"/>
     <col width="50" customWidth="1" min="8" max="8"/>
     <col width="70" customWidth="1" min="9" max="9"/>
-    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
     <col width="30" customWidth="1" min="11" max="11"/>
     <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,12 +467,12 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Page T1</t>
+          <t>Page (trimestre précédent)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Page T2</t>
+          <t>Page (trimestre courant)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
@@ -488,12 +487,12 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T1</t>
+          <t>Libellé (trimestre précédent)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Libellé T2</t>
+          <t>Libellé (trimestre courant)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -503,7 +502,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Nouvelle divulgation ?</t>
+          <t>Nouvelle idée ?</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -517,18 +516,13 @@
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Validé par</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Validé le</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N1"/>
+  <autoFilter ref="A1:M1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>